--- a/Sources/Ayat_Takheen_Export.xlsx
+++ b/Sources/Ayat_Takheen_Export.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30604"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Global\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7aa1d8f405ba1d72/NDEDC_Production/Sources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB87E765-80B2-47CB-8179-5826F3EBF703}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{FB87E765-80B2-47CB-8179-5826F3EBF703}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4098FD21-F271-411B-BF36-9A4748093274}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="330" windowWidth="24240" windowHeight="13290" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13056" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ayat_Takheen Data" sheetId="1" r:id="rId1"/>
@@ -672,7 +672,7 @@
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1042,9 +1042,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B347"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="13.90625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -3656,89 +3657,54 @@
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A327"/>
-      <c r="B327"/>
+      <c r="A327" s="1">
+        <v>60065361</v>
+      </c>
+      <c r="B327" s="1">
+        <v>20</v>
+      </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A328"/>
-      <c r="B328"/>
+      <c r="A328" s="1">
+        <v>44852950</v>
+      </c>
+      <c r="B328" s="1">
+        <v>20</v>
+      </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A329"/>
-      <c r="B329"/>
+      <c r="A329" s="1">
+        <v>38614101</v>
+      </c>
+      <c r="B329" s="1">
+        <v>20</v>
+      </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A330"/>
-      <c r="B330"/>
-    </row>
-    <row r="331" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A331"/>
-      <c r="B331"/>
-    </row>
-    <row r="332" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A332"/>
-      <c r="B332"/>
-    </row>
-    <row r="333" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A333"/>
-      <c r="B333"/>
-    </row>
-    <row r="334" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A334"/>
-      <c r="B334"/>
-    </row>
-    <row r="335" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A335"/>
-      <c r="B335"/>
-    </row>
-    <row r="336" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A336"/>
-      <c r="B336"/>
-    </row>
-    <row r="337" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A337"/>
-      <c r="B337"/>
-    </row>
-    <row r="338" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A338"/>
-      <c r="B338"/>
-    </row>
-    <row r="339" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A339"/>
-      <c r="B339"/>
-    </row>
-    <row r="340" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A340"/>
-      <c r="B340"/>
-    </row>
-    <row r="341" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A341"/>
-      <c r="B341"/>
-    </row>
-    <row r="342" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A342"/>
-      <c r="B342"/>
-    </row>
-    <row r="343" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A343"/>
-      <c r="B343"/>
-    </row>
-    <row r="344" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A344"/>
-      <c r="B344"/>
-    </row>
-    <row r="345" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A345"/>
-      <c r="B345"/>
-    </row>
-    <row r="346" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A346"/>
-      <c r="B346"/>
-    </row>
-    <row r="347" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A347"/>
-      <c r="B347"/>
-    </row>
+      <c r="A330" s="1">
+        <v>2420861</v>
+      </c>
+      <c r="B330" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="331" spans="1:2" x14ac:dyDescent="0.25"/>
+    <row r="332" spans="1:2" x14ac:dyDescent="0.25"/>
+    <row r="333" spans="1:2" x14ac:dyDescent="0.25"/>
+    <row r="334" spans="1:2" x14ac:dyDescent="0.25"/>
+    <row r="335" spans="1:2" x14ac:dyDescent="0.25"/>
+    <row r="336" spans="1:2" x14ac:dyDescent="0.25"/>
+    <row r="337" x14ac:dyDescent="0.25"/>
+    <row r="338" x14ac:dyDescent="0.25"/>
+    <row r="339" x14ac:dyDescent="0.25"/>
+    <row r="340" x14ac:dyDescent="0.25"/>
+    <row r="341" x14ac:dyDescent="0.25"/>
+    <row r="342" x14ac:dyDescent="0.25"/>
+    <row r="343" x14ac:dyDescent="0.25"/>
+    <row r="344" x14ac:dyDescent="0.25"/>
+    <row r="345" x14ac:dyDescent="0.25"/>
+    <row r="346" x14ac:dyDescent="0.25"/>
+    <row r="347" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
